--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/08 11:30:43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23529.41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>23529.41</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22529.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/08 14:14:50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22529</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/08 11:30:43</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>23529.41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>23529</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22529.41</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/08 11:28:20</t>
+          <t>07/13 12:08:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>20833.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/08 14:14:50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>22529</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/08 11:30:43</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20833.33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23529.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>23529</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.41</t>
+          <t>20833.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/13 13:37:23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>60975.61</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/13 12:08:49</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>175000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>20833.33</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>175000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20833.33</t>
+          <t>675000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81808.94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20833.33</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>81808.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/13 15:24:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>81808</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>675000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>81808.94</t>
+          <t>675000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81808.94</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>81808</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>81808.94</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/13 13:37:23</t>
+          <t>07/15 19:21:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/13 12:08:49</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>175000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20833.33</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/13 15:24:33</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>81808</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>60975.61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>675000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>81808.94</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>81808</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.94</t>
+          <t>60975.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/15 20:32:10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>60975</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60975.61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>60975</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>60975.61</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 19:21:17</t>
+          <t>08/19 14:13:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/15 20:32:10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>60975</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>18072.29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60975.61</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>60975</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.61</t>
+          <t>18072.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/19 15:39:23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18072</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18072.29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18072</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18072.29</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.29</t>
         </is>
       </c>
     </row>
